--- a/Таблицы/Типы данных.xlsx
+++ b/Таблицы/Типы данных.xlsx
@@ -8,12 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Политех\4 семестр\БД\Таблицы\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38EE545C-CD02-4C74-B19E-D1CDE78F8A2F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F519405C-7197-4D4A-86BE-D34DEE098350}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="Объект" sheetId="1" r:id="rId1"/>
+    <sheet name="Образовательное" sheetId="2" r:id="rId2"/>
+    <sheet name="Учёный" sheetId="3" r:id="rId3"/>
+    <sheet name="Исследовательская" sheetId="4" r:id="rId4"/>
+    <sheet name="Телескоп" sheetId="6" r:id="rId5"/>
+    <sheet name="Астрономы" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="51">
   <si>
     <t>Название</t>
   </si>
@@ -57,9 +62,6 @@
     <t>Видимый размер</t>
   </si>
   <si>
-    <t>Name</t>
-  </si>
-  <si>
     <t>Type</t>
   </si>
   <si>
@@ -72,17 +74,122 @@
     <t>NOT NULL</t>
   </si>
   <si>
-    <t>VARCHAR</t>
-  </si>
-  <si>
     <t>DECIMAL</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>PK</t>
+  </si>
+  <si>
+    <t>FP</t>
+  </si>
+  <si>
+    <t>Страна</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>Бюджет</t>
+  </si>
+  <si>
+    <t>Budget</t>
+  </si>
+  <si>
+    <t>ФИО</t>
+  </si>
+  <si>
+    <t>Организация</t>
+  </si>
+  <si>
+    <t>Специальность</t>
+  </si>
+  <si>
+    <t>Учёная степень</t>
+  </si>
+  <si>
+    <t>Graduate</t>
+  </si>
+  <si>
+    <t>Organisation</t>
+  </si>
+  <si>
+    <t>Person</t>
+  </si>
+  <si>
+    <t>Object</t>
+  </si>
+  <si>
+    <t>Возраст</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Тип финансирования</t>
+  </si>
+  <si>
+    <t>Организация-владелец</t>
+  </si>
+  <si>
+    <t>Telescope</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>Год введения в эксплуатацию</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Место развёртывания</t>
+  </si>
+  <si>
+    <t>Spot</t>
+  </si>
+  <si>
+    <t>Величина</t>
+  </si>
+  <si>
+    <t>Magnitude</t>
+  </si>
+  <si>
+    <t>VARCHAR(55)</t>
+  </si>
+  <si>
+    <t>VARCHAR(48)</t>
+  </si>
+  <si>
+    <t>VARCHAR(100)</t>
+  </si>
+  <si>
+    <t>VARCHAR(3)</t>
+  </si>
+  <si>
+    <t>VARCHAR(32)</t>
+  </si>
+  <si>
+    <t>VARCHAR(40)</t>
+  </si>
+  <si>
+    <t>VARCHAR(15)</t>
+  </si>
+  <si>
+    <t>VARCHAR(20)</t>
+  </si>
+  <si>
+    <t>VARCHAR(30)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -96,6 +203,15 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -105,7 +221,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -113,13 +229,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -400,7 +534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.6640625" customWidth="1"/>
@@ -411,83 +545,735 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="C3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="D4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="D5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
+      <c r="D6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE7D3666-9D66-40D1-B11C-ADB0C0CC8AB6}">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.44140625" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" customWidth="1"/>
+    <col min="5" max="5" width="10.44140625" customWidth="1"/>
+    <col min="6" max="6" width="9.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AD596AA-2A6C-4EA4-B9A0-722E37EEAB5F}">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.77734375" customWidth="1"/>
+    <col min="2" max="2" width="11.88671875" customWidth="1"/>
+    <col min="3" max="3" width="12.77734375" customWidth="1"/>
+    <col min="4" max="4" width="4.44140625" customWidth="1"/>
+    <col min="6" max="6" width="9.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC834E55-4734-47A2-A950-2C9726830506}">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="2" max="3" width="12.44140625" customWidth="1"/>
+    <col min="4" max="4" width="5.21875" customWidth="1"/>
+    <col min="5" max="5" width="9.77734375" customWidth="1"/>
+    <col min="6" max="6" width="9.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A92DD766-3E18-44E5-A96B-8279B97F6BCB}">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="26.44140625" customWidth="1"/>
+    <col min="2" max="2" width="11.88671875" customWidth="1"/>
+    <col min="3" max="3" width="12.77734375" customWidth="1"/>
+    <col min="4" max="4" width="4.44140625" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="9.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B52233BF-38E9-4FEB-AB82-E40DE0606C82}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.33203125" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="12.21875" customWidth="1"/>
+    <col min="4" max="4" width="3.88671875" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" customWidth="1"/>
+    <col min="6" max="6" width="9.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Таблицы/Типы данных.xlsx
+++ b/Таблицы/Типы данных.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Политех\4 семестр\БД\Таблицы\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F519405C-7197-4D4A-86BE-D34DEE098350}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D528605-C74D-44D3-B087-78A2C0AD9CEA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Объект" sheetId="1" r:id="rId1"/>
-    <sheet name="Образовательное" sheetId="2" r:id="rId2"/>
+    <sheet name="Образовательное учреждение" sheetId="2" r:id="rId2"/>
     <sheet name="Учёный" sheetId="3" r:id="rId3"/>
-    <sheet name="Исследовательская" sheetId="4" r:id="rId4"/>
-    <sheet name="Телескоп" sheetId="6" r:id="rId5"/>
+    <sheet name="Исследовательская организация" sheetId="4" r:id="rId4"/>
+    <sheet name="Автоматический телескоп" sheetId="6" r:id="rId5"/>
     <sheet name="Астрономы" sheetId="5" r:id="rId6"/>
+    <sheet name="Каталог" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="59">
   <si>
     <t>Название</t>
   </si>
@@ -101,9 +102,6 @@
     <t>ФИО</t>
   </si>
   <si>
-    <t>Организация</t>
-  </si>
-  <si>
     <t>Специальность</t>
   </si>
   <si>
@@ -131,15 +129,9 @@
     <t>Тип финансирования</t>
   </si>
   <si>
-    <t>Организация-владелец</t>
-  </si>
-  <si>
     <t>Telescope</t>
   </si>
   <si>
-    <t>Owner</t>
-  </si>
-  <si>
     <t>Год введения в эксплуатацию</t>
   </si>
   <si>
@@ -183,6 +175,39 @@
   </si>
   <si>
     <t>VARCHAR(30)</t>
+  </si>
+  <si>
+    <t>ID-каталога</t>
+  </si>
+  <si>
+    <t>ID-организации</t>
+  </si>
+  <si>
+    <t>ID_Organisation</t>
+  </si>
+  <si>
+    <t>ID_Catalog</t>
+  </si>
+  <si>
+    <t>Количество:</t>
+  </si>
+  <si>
+    <t>Количество объектов</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>CatalogName</t>
+  </si>
+  <si>
+    <t>Proffesion</t>
+  </si>
+  <si>
+    <t>Порядок:</t>
+  </si>
+  <si>
+    <t>Порядок</t>
   </si>
 </sst>
 </file>
@@ -221,7 +246,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -244,16 +269,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -534,7 +569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.6640625" customWidth="1"/>
@@ -542,9 +577,10 @@
     <col min="3" max="3" width="12.33203125" customWidth="1"/>
     <col min="5" max="5" width="9.6640625" customWidth="1"/>
     <col min="6" max="6" width="9.5546875" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
@@ -563,16 +599,22 @@
       <c r="F1" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>50</v>
+      <c r="H1" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>15</v>
@@ -583,8 +625,14 @@
       <c r="F2" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -592,7 +640,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>15</v>
@@ -604,7 +652,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -624,7 +672,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -644,12 +692,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>14</v>
@@ -661,6 +709,26 @@
         <v>17</v>
       </c>
       <c r="F6" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
@@ -672,17 +740,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE7D3666-9D66-40D1-B11C-ADB0C0CC8AB6}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.44140625" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" customWidth="1"/>
     <col min="3" max="3" width="12.5546875" customWidth="1"/>
     <col min="5" max="5" width="10.44140625" customWidth="1"/>
     <col min="6" max="6" width="9.77734375" customWidth="1"/>
+    <col min="8" max="8" width="11.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
@@ -701,16 +770,22 @@
       <c r="F1" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H1" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>15</v>
@@ -721,8 +796,14 @@
       <c r="F2" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -730,7 +811,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>15</v>
@@ -742,7 +823,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
@@ -750,7 +831,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>15</v>
@@ -762,7 +843,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>20</v>
       </c>
@@ -779,6 +860,26 @@
         <v>17</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>13</v>
       </c>
     </row>
@@ -789,17 +890,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AD596AA-2A6C-4EA4-B9A0-722E37EEAB5F}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.77734375" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" customWidth="1"/>
+    <col min="2" max="2" width="13.77734375" customWidth="1"/>
     <col min="3" max="3" width="12.77734375" customWidth="1"/>
     <col min="4" max="4" width="4.44140625" customWidth="1"/>
     <col min="6" max="6" width="9.44140625" customWidth="1"/>
+    <col min="8" max="8" width="11.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
@@ -818,16 +920,22 @@
       <c r="F1" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H1" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>15</v>
@@ -838,36 +946,42 @@
       <c r="F2" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>19</v>
+      <c r="B4" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>15</v>
@@ -879,35 +993,35 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>25</v>
-      </c>
       <c r="B6" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>15</v>
@@ -916,6 +1030,26 @@
         <v>17</v>
       </c>
       <c r="F6" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
@@ -926,17 +1060,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC834E55-4734-47A2-A950-2C9726830506}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
-    <col min="2" max="3" width="12.44140625" customWidth="1"/>
+    <col min="2" max="2" width="14.5546875" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" customWidth="1"/>
     <col min="4" max="4" width="5.21875" customWidth="1"/>
     <col min="5" max="5" width="9.77734375" customWidth="1"/>
     <col min="6" max="6" width="9.6640625" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
@@ -955,16 +1091,22 @@
       <c r="F1" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H1" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>15</v>
@@ -975,16 +1117,22 @@
       <c r="F2" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>15</v>
@@ -996,7 +1144,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
@@ -1004,7 +1152,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>15</v>
@@ -1016,7 +1164,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>20</v>
       </c>
@@ -1033,6 +1181,26 @@
         <v>17</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1043,18 +1211,19 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A92DD766-3E18-44E5-A96B-8279B97F6BCB}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.44140625" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" customWidth="1"/>
     <col min="3" max="3" width="12.77734375" customWidth="1"/>
     <col min="4" max="4" width="4.44140625" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="9.88671875" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
@@ -1073,16 +1242,22 @@
       <c r="F1" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H1" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>15</v>
@@ -1093,8 +1268,14 @@
       <c r="F2" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -1102,7 +1283,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>15</v>
@@ -1114,32 +1295,32 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="B5" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>14</v>
@@ -1154,15 +1335,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>15</v>
@@ -1171,6 +1352,26 @@
         <v>17</v>
       </c>
       <c r="F6" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1182,18 +1383,19 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B52233BF-38E9-4FEB-AB82-E40DE0606C82}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" customWidth="1"/>
     <col min="3" max="3" width="12.21875" customWidth="1"/>
     <col min="4" max="4" width="3.88671875" customWidth="1"/>
     <col min="5" max="5" width="10.109375" customWidth="1"/>
     <col min="6" max="6" width="9.33203125" customWidth="1"/>
+    <col min="8" max="8" width="11.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
@@ -1212,16 +1414,22 @@
       <c r="F1" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H1" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>15</v>
@@ -1232,8 +1440,14 @@
       <c r="F2" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>18</v>
       </c>
@@ -1241,7 +1455,7 @@
         <v>19</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>15</v>
@@ -1253,15 +1467,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="C4" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>15</v>
@@ -1270,10 +1484,159 @@
         <v>17</v>
       </c>
       <c r="F4" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0DC64E4-BB25-40C1-8B32-0B71D9D42E39}">
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20.109375" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="6" max="6" width="9.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>